--- a/rules/CORE-000747/positive/01/data/unit-test-coreid-FB6001-positive_01.xlsx
+++ b/rules/CORE-000747/positive/01/data/unit-test-coreid-FB6001-positive_01.xlsx
@@ -1379,7 +1379,7 @@
     <row r="5">
       <c r="A5" s="14" t="inlineStr">
         <is>
-          <t>CDISC-TEST</t>
+          <t>CDISCCORE01</t>
         </is>
       </c>
       <c r="B5" s="14" t="inlineStr">
@@ -1400,7 +1400,7 @@
       <c r="G5" s="15" t="n"/>
       <c r="H5" s="16" t="inlineStr">
         <is>
-          <t>HATIAN or NEGRO</t>
+          <t>HAITIAN</t>
         </is>
       </c>
       <c r="I5" s="14" t="inlineStr">
@@ -1412,7 +1412,7 @@
     <row r="6">
       <c r="A6" s="14" t="inlineStr">
         <is>
-          <t>CDISC-TEST</t>
+          <t>CDISCCORE01</t>
         </is>
       </c>
       <c r="B6" s="14" t="inlineStr">
@@ -1433,7 +1433,7 @@
       <c r="G6" s="15" t="n"/>
       <c r="H6" s="16" t="inlineStr">
         <is>
-          <t>HATIAN or NEGRO</t>
+          <t>NEGRO</t>
         </is>
       </c>
       <c r="I6" s="14" t="inlineStr">
